--- a/monitoring_forms/019_monitoring_refusal_form--monitoring_forms.xlsx
+++ b/monitoring_forms/019_monitoring_refusal_form--monitoring_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable',_'value':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable', 'value': 'not_applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'not_known',_'value':_'not_known'}</t>
+          <t>not_known</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Not Known', 'value': 'not_known'}</t>
+          <t>Not Known</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'refusal',_'value':_'refusal'}</t>
+          <t>refusal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Refusal', 'value': 'refusal'}</t>
+          <t>Refusal</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'active',_'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Active', 'value': 'active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'closed',_'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Closed', 'value': 'closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'refused',_'value':_'refused'}</t>
+          <t>refused</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Refused', 'value': 'refused'}</t>
+          <t>Refused</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'user_1',_'value':_'user_1'}</t>
+          <t>user_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'User 1', 'value': 'user_1'}</t>
+          <t>User 1</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'user_2',_'value':_'user_2'}</t>
+          <t>user_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'User 2', 'value': 'user_2'}</t>
+          <t>User 2</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'call',_'value':_'call'}</t>
+          <t>call</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Call', 'value': 'call'}</t>
+          <t>Call</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Email', 'value': 'email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'sms',_'value':_'sms'}</t>
+          <t>sms</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'SMS', 'value': 'sms'}</t>
+          <t>SMS</t>
         </is>
       </c>
     </row>
